--- a/exports/trend_1d/INDUSINDBK_full_report.xlsx
+++ b/exports/trend_1d/INDUSINDBK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.25</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42110</v>
+        <v>42111</v>
       </c>
       <c r="H2" t="n">
-        <v>934.45</v>
+        <v>876</v>
       </c>
       <c r="I2" t="n">
         <v>878.3200843708964</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K2" t="n">
-        <v>12.54</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
         <v>2.05</v>
@@ -555,7 +578,7 @@
         <v>1.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.24</v>
+        <v>6.26</v>
       </c>
       <c r="O2" t="n">
         <v>1.68</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.24</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H3" t="n">
-        <v>855.3</v>
+        <v>873.95</v>
       </c>
       <c r="I3" t="n">
         <v>873.5136102191587</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K3" t="n">
-        <v>2.36</v>
+        <v>0.23</v>
       </c>
       <c r="L3" t="n">
         <v>6.85</v>
@@ -612,7 +647,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>-6.26</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.06</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42160</v>
+        <v>42163</v>
       </c>
       <c r="H4" t="n">
-        <v>834.45</v>
+        <v>811.7</v>
       </c>
       <c r="I4" t="n">
         <v>816.2778940571008</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.52</v>
+        <v>-7.12</v>
       </c>
       <c r="L4" t="n">
-        <v>5.03</v>
+        <v>7.43</v>
       </c>
       <c r="M4" t="n">
         <v>0.79</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42184</v>
+        <v>42185</v>
       </c>
       <c r="H5" t="n">
-        <v>859.6</v>
+        <v>872.7</v>
       </c>
       <c r="I5" t="n">
         <v>870.4887580276578</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.9</v>
+        <v>-7.52</v>
       </c>
       <c r="L5" t="n">
         <v>9.09</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H6" t="n">
-        <v>950.7</v>
+        <v>914.45</v>
       </c>
       <c r="I6" t="n">
         <v>915.2312721819795</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" t="n">
-        <v>8.94</v>
+        <v>4.78</v>
       </c>
       <c r="L6" t="n">
         <v>2.03</v>
@@ -783,7 +854,7 @@
         <v>1.89</v>
       </c>
       <c r="N6" t="n">
-        <v>2.21</v>
+        <v>3.81</v>
       </c>
       <c r="O6" t="n">
         <v>1.52</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42263</v>
+        <v>42265</v>
       </c>
       <c r="H7" t="n">
-        <v>899.1</v>
+        <v>918.65</v>
       </c>
       <c r="I7" t="n">
         <v>915.7924897785097</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K7" t="n">
-        <v>1.68</v>
+        <v>-0.46</v>
       </c>
       <c r="L7" t="n">
         <v>6.24</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42317</v>
+        <v>42318</v>
       </c>
       <c r="H8" t="n">
-        <v>923.4</v>
+        <v>893.75</v>
       </c>
       <c r="I8" t="n">
         <v>907.2384892409787</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K8" t="n">
-        <v>0.52</v>
+        <v>-2.71</v>
       </c>
       <c r="L8" t="n">
         <v>4.97</v>
@@ -897,7 +992,7 @@
         <v>1.95</v>
       </c>
       <c r="N8" t="n">
-        <v>3.12</v>
+        <v>3.21</v>
       </c>
       <c r="O8" t="n">
         <v>2.17</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.6</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42340</v>
+        <v>42341</v>
       </c>
       <c r="H9" t="n">
-        <v>942.6</v>
+        <v>946.7</v>
       </c>
       <c r="I9" t="n">
         <v>944.8157220552738</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.47</v>
+        <v>-5.92</v>
       </c>
       <c r="L9" t="n">
-        <v>5.73</v>
+        <v>6.24</v>
       </c>
       <c r="M9" t="n">
         <v>0.88</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.64</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42380</v>
+        <v>42381</v>
       </c>
       <c r="H10" t="n">
-        <v>936.75</v>
+        <v>913.25</v>
       </c>
       <c r="I10" t="n">
         <v>921.9939959792463</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.05</v>
+        <v>-3.53</v>
       </c>
       <c r="L10" t="n">
         <v>4.54</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.78</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H11" t="n">
-        <v>860.8</v>
+        <v>882.6</v>
       </c>
       <c r="I11" t="n">
         <v>879.8106667629951</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K11" t="n">
-        <v>5.74</v>
+        <v>3.36</v>
       </c>
       <c r="L11" t="n">
         <v>5.12</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H12" t="n">
-        <v>1192.35</v>
+        <v>1093.1</v>
       </c>
       <c r="I12" t="n">
         <v>1158.833624719218</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K12" t="n">
-        <v>35.1</v>
+        <v>23.85</v>
       </c>
       <c r="L12" t="n">
         <v>1.31</v>
@@ -1125,7 +1268,7 @@
         <v>4.64</v>
       </c>
       <c r="N12" t="n">
-        <v>2.37</v>
+        <v>8.32</v>
       </c>
       <c r="O12" t="n">
         <v>2.53</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>14.67</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42740</v>
+        <v>42741</v>
       </c>
       <c r="H13" t="n">
-        <v>1127.55</v>
+        <v>1144.05</v>
       </c>
       <c r="I13" t="n">
         <v>1139.578486923447</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.15</v>
+        <v>-4.66</v>
       </c>
       <c r="L13" t="n">
         <v>9.77</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.28</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H14" t="n">
-        <v>1406.6</v>
+        <v>1389.25</v>
       </c>
       <c r="I14" t="n">
         <v>1401.670671660341</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K14" t="n">
-        <v>22.95</v>
+        <v>21.43</v>
       </c>
       <c r="L14" t="n">
         <v>1.2</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.21</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42880</v>
+        <v>42881</v>
       </c>
       <c r="H15" t="n">
-        <v>1461.6</v>
+        <v>1477.7</v>
       </c>
       <c r="I15" t="n">
         <v>1465.310677993298</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.21</v>
+        <v>-6.37</v>
       </c>
       <c r="L15" t="n">
-        <v>5.96</v>
+        <v>6.88</v>
       </c>
       <c r="M15" t="n">
         <v>0.72</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.61</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H16" t="n">
-        <v>1664.9</v>
+        <v>1592.4</v>
       </c>
       <c r="I16" t="n">
         <v>1653.389511811107</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K16" t="n">
-        <v>12.67</v>
+        <v>7.76</v>
       </c>
       <c r="L16" t="n">
         <v>1.69</v>
@@ -1353,7 +1544,7 @@
         <v>1.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>4.35</v>
       </c>
       <c r="O16" t="n">
         <v>1.1</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.49</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43105</v>
+        <v>43108</v>
       </c>
       <c r="H17" t="n">
-        <v>1698.2</v>
+        <v>1719.9</v>
       </c>
       <c r="I17" t="n">
         <v>1706.563987216184</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.64</v>
+        <v>-8.01</v>
       </c>
       <c r="L17" t="n">
-        <v>6.95</v>
+        <v>8.26</v>
       </c>
       <c r="M17" t="n">
         <v>1.76</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.38</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="H18" t="n">
-        <v>1682.85</v>
+        <v>1661.75</v>
       </c>
       <c r="I18" t="n">
         <v>1663.420258939277</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.15</v>
+        <v>-3.38</v>
       </c>
       <c r="L18" t="n">
         <v>4.38</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.13</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43173</v>
+        <v>43174</v>
       </c>
       <c r="H19" t="n">
-        <v>1733.35</v>
+        <v>1741.75</v>
       </c>
       <c r="I19" t="n">
         <v>1736.16977559564</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.31</v>
+        <v>-4.81</v>
       </c>
       <c r="L19" t="n">
         <v>5.37</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.15</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43340</v>
+        <v>43341</v>
       </c>
       <c r="H20" t="n">
-        <v>1933.65</v>
+        <v>1905.55</v>
       </c>
       <c r="I20" t="n">
         <v>1920.762259814445</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K20" t="n">
-        <v>11.02</v>
+        <v>9.4</v>
       </c>
       <c r="L20" t="n">
         <v>2.28</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.62</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43430</v>
+        <v>43431</v>
       </c>
       <c r="H21" t="n">
-        <v>1562.75</v>
+        <v>1588.55</v>
       </c>
       <c r="I21" t="n">
         <v>1578.957906991949</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K21" t="n">
-        <v>17.99</v>
+        <v>16.64</v>
       </c>
       <c r="L21" t="n">
         <v>1.77</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>10.52</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43476</v>
+        <v>43479</v>
       </c>
       <c r="H22" t="n">
-        <v>1515.15</v>
+        <v>1484.05</v>
       </c>
       <c r="I22" t="n">
         <v>1509.26770504415</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.62</v>
+        <v>-6.58</v>
       </c>
       <c r="L22" t="n">
-        <v>7.15</v>
+        <v>7.4</v>
       </c>
       <c r="M22" t="n">
         <v>5</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43535</v>
+        <v>43536</v>
       </c>
       <c r="H23" t="n">
-        <v>1514.6</v>
+        <v>1569.05</v>
       </c>
       <c r="I23" t="n">
         <v>1555.235681453353</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.06</v>
+        <v>-5.73</v>
       </c>
       <c r="L23" t="n">
-        <v>4.93</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
         <v>0.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.73</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
         <v>-2.05</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43577</v>
+        <v>43578</v>
       </c>
       <c r="H24" t="n">
-        <v>1691</v>
+        <v>1651.35</v>
       </c>
       <c r="I24" t="n">
         <v>1672.983648139416</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K24" t="n">
-        <v>7.77</v>
+        <v>5.25</v>
       </c>
       <c r="L24" t="n">
         <v>3.72</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.25</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43607</v>
+        <v>43608</v>
       </c>
       <c r="H25" t="n">
-        <v>1518.9</v>
+        <v>1598.75</v>
       </c>
       <c r="I25" t="n">
         <v>1522.583735112591</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>8.02</v>
+        <v>3.19</v>
       </c>
       <c r="L25" t="n">
         <v>4.4</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>14.45</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43629</v>
+        <v>43630</v>
       </c>
       <c r="H26" t="n">
-        <v>1488.85</v>
+        <v>1426.8</v>
       </c>
       <c r="I26" t="n">
         <v>1471.295816331948</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.87</v>
+        <v>-10.76</v>
       </c>
       <c r="L26" t="n">
-        <v>9.93</v>
+        <v>11.73</v>
       </c>
       <c r="M26" t="n">
         <v>3.18</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>16.55</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H27" t="n">
-        <v>1419.6</v>
+        <v>1511.55</v>
       </c>
       <c r="I27" t="n">
         <v>1443.888023027233</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5</v>
+        <v>-5.94</v>
       </c>
       <c r="L27" t="n">
         <v>9.51</v>
       </c>
       <c r="M27" t="n">
-        <v>2.71</v>
+        <v>2.99</v>
       </c>
       <c r="N27" t="n">
         <v>10.71</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>13.65</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43738</v>
+        <v>43739</v>
       </c>
       <c r="H28" t="n">
-        <v>1383.55</v>
+        <v>1298.05</v>
       </c>
       <c r="I28" t="n">
         <v>1354.779074532649</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.470000000000001</v>
+        <v>-14.12</v>
       </c>
       <c r="L28" t="n">
-        <v>10.94</v>
+        <v>21.4</v>
       </c>
       <c r="M28" t="n">
         <v>0.54</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>19.35</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43777</v>
+        <v>43780</v>
       </c>
       <c r="H29" t="n">
-        <v>1422.8</v>
+        <v>1445.05</v>
       </c>
       <c r="I29" t="n">
         <v>1439.326326351069</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K29" t="n">
-        <v>-9.609999999999999</v>
+        <v>-11.32</v>
       </c>
       <c r="L29" t="n">
-        <v>12.01</v>
+        <v>12.08</v>
       </c>
       <c r="M29" t="n">
         <v>1.95</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>12.6</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43808</v>
+        <v>43809</v>
       </c>
       <c r="H30" t="n">
-        <v>1450</v>
+        <v>1411.6</v>
       </c>
       <c r="I30" t="n">
         <v>1440.719483343191</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K30" t="n">
-        <v>0.34</v>
+        <v>-2.31</v>
       </c>
       <c r="L30" t="n">
         <v>6.88</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.49</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H31" t="n">
-        <v>422.35</v>
+        <v>451.6</v>
       </c>
       <c r="I31" t="n">
         <v>439.8003429136267</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K31" t="n">
-        <v>70.08</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="L31" t="n">
         <v>12.28</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>7</v>
+      </c>
+      <c r="U31" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>19.37</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H32" t="n">
-        <v>560.6</v>
+        <v>544</v>
       </c>
       <c r="I32" t="n">
         <v>559.066804933022</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K32" t="n">
-        <v>24.14</v>
+        <v>20.46</v>
       </c>
       <c r="L32" t="n">
         <v>1.68</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>20.41</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44109</v>
+        <v>44110</v>
       </c>
       <c r="H33" t="n">
-        <v>601.55</v>
+        <v>622.8</v>
       </c>
       <c r="I33" t="n">
         <v>603.2989495251005</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.58</v>
+        <v>-14.49</v>
       </c>
       <c r="L33" t="n">
         <v>15.94</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>18.25</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H34" t="n">
-        <v>905.2</v>
+        <v>842.7</v>
       </c>
       <c r="I34" t="n">
         <v>844.9839839819801</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K34" t="n">
-        <v>45.34</v>
+        <v>35.31</v>
       </c>
       <c r="L34" t="n">
         <v>8.32</v>
@@ -2379,7 +2786,7 @@
         <v>1.48</v>
       </c>
       <c r="N34" t="n">
-        <v>5.66</v>
+        <v>6.9</v>
       </c>
       <c r="O34" t="n">
         <v>3.53</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>15.21</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44202</v>
+        <v>44203</v>
       </c>
       <c r="H35" t="n">
-        <v>922.35</v>
+        <v>952.05</v>
       </c>
       <c r="I35" t="n">
         <v>948.2245256771365</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.449999999999999</v>
+        <v>-12.98</v>
       </c>
       <c r="L35" t="n">
-        <v>11.16</v>
+        <v>14.12</v>
       </c>
       <c r="M35" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="N35" t="n">
         <v>5.3</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>10.77</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H36" t="n">
-        <v>893.3</v>
+        <v>849.15</v>
       </c>
       <c r="I36" t="n">
         <v>870.6842906502488</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K36" t="n">
-        <v>-6.17</v>
+        <v>-10.81</v>
       </c>
       <c r="L36" t="n">
-        <v>6.52</v>
+        <v>11.85</v>
       </c>
       <c r="M36" t="n">
         <v>0.98</v>
       </c>
       <c r="N36" t="n">
-        <v>3.52</v>
+        <v>4.94</v>
       </c>
       <c r="O36" t="n">
         <v>3.22</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>16.6</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44225</v>
+        <v>44228</v>
       </c>
       <c r="H37" t="n">
-        <v>846.1</v>
+        <v>970.6</v>
       </c>
       <c r="I37" t="n">
         <v>928.2660449082083</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>0.36</v>
+        <v>-14.3</v>
       </c>
       <c r="L37" t="n">
-        <v>7.44</v>
+        <v>15.57</v>
       </c>
       <c r="M37" t="n">
         <v>1.81</v>
       </c>
       <c r="N37" t="n">
-        <v>5.42</v>
+        <v>14.71</v>
       </c>
       <c r="O37" t="n">
         <v>-4.94</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>21.11</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44274</v>
+        <v>44277</v>
       </c>
       <c r="H38" t="n">
-        <v>1011.9</v>
+        <v>968.15</v>
       </c>
       <c r="I38" t="n">
         <v>969.2649202759237</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>4.26</v>
+        <v>-0.25</v>
       </c>
       <c r="L38" t="n">
         <v>11.81</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>14.73</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H39" t="n">
-        <v>926.2</v>
+        <v>945.4</v>
       </c>
       <c r="I39" t="n">
         <v>940.7980432785132</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K39" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="L39" t="n">
         <v>4.51</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.16</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H40" t="n">
-        <v>1015.85</v>
+        <v>981.55</v>
       </c>
       <c r="I40" t="n">
         <v>994.9577725312529</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K40" t="n">
-        <v>7.45</v>
+        <v>3.82</v>
       </c>
       <c r="L40" t="n">
         <v>6.06</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.24</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44453</v>
+        <v>44454</v>
       </c>
       <c r="H41" t="n">
-        <v>1036.6</v>
+        <v>1053.95</v>
       </c>
       <c r="I41" t="n">
         <v>1050.659538446705</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.61</v>
+        <v>-7.38</v>
       </c>
       <c r="L41" t="n">
-        <v>7.48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>1.87</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.91</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44504</v>
+        <v>44508</v>
       </c>
       <c r="H42" t="n">
-        <v>1189.1</v>
+        <v>1061.15</v>
       </c>
       <c r="I42" t="n">
         <v>1104.491442019149</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K42" t="n">
-        <v>12.82</v>
+        <v>0.68</v>
       </c>
       <c r="L42" t="n">
         <v>2.51</v>
       </c>
       <c r="M42" t="n">
-        <v>1.33</v>
+        <v>4.97</v>
       </c>
       <c r="N42" t="n">
-        <v>3.54</v>
+        <v>10.76</v>
       </c>
       <c r="O42" t="n">
         <v>1.67</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>18.46</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H43" t="n">
-        <v>917.95</v>
+        <v>941.55</v>
       </c>
       <c r="I43" t="n">
         <v>933.1627202963726</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K43" t="n">
-        <v>13.49</v>
+        <v>11.27</v>
       </c>
       <c r="L43" t="n">
         <v>6.49</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.32</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H44" t="n">
-        <v>877.2</v>
+        <v>854.1</v>
       </c>
       <c r="I44" t="n">
         <v>859.2191670981035</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.83</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>7.39</v>
+        <v>10.24</v>
       </c>
       <c r="M44" t="n">
         <v>0.86</v>
       </c>
       <c r="N44" t="n">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="O44" t="n">
         <v>2.57</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.56</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H45" t="n">
-        <v>922.3</v>
+        <v>975.35</v>
       </c>
       <c r="I45" t="n">
         <v>930.8100690613951</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.99</v>
+        <v>-14.2</v>
       </c>
       <c r="L45" t="n">
-        <v>8.59</v>
+        <v>14.95</v>
       </c>
       <c r="M45" t="n">
         <v>2.65</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>13.55</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44624</v>
+        <v>44627</v>
       </c>
       <c r="H46" t="n">
-        <v>901.9</v>
+        <v>834.4</v>
       </c>
       <c r="I46" t="n">
         <v>873.2457667772312</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.53</v>
+        <v>-14.45</v>
       </c>
       <c r="L46" t="n">
-        <v>10.92</v>
+        <v>15.36</v>
       </c>
       <c r="M46" t="n">
         <v>3.28</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>16.93</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H47" t="n">
-        <v>935.4</v>
+        <v>968.6</v>
       </c>
       <c r="I47" t="n">
         <v>944.438216910214</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.1</v>
+        <v>-16.08</v>
       </c>
       <c r="L47" t="n">
-        <v>13.79</v>
+        <v>16.37</v>
       </c>
       <c r="M47" t="n">
         <v>3.94</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>10.54</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H48" t="n">
-        <v>915.4</v>
+        <v>889.7</v>
       </c>
       <c r="I48" t="n">
         <v>915.0435445966298</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.49</v>
+        <v>-8.15</v>
       </c>
       <c r="L48" t="n">
-        <v>6.82</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>1.9</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.7</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44761</v>
+        <v>44762</v>
       </c>
       <c r="H49" t="n">
-        <v>868.1</v>
+        <v>879.3</v>
       </c>
       <c r="I49" t="n">
         <v>872.6457572139147</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K49" t="n">
-        <v>2.43</v>
+        <v>1.17</v>
       </c>
       <c r="L49" t="n">
         <v>7.2</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.9</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44831</v>
+        <v>44832</v>
       </c>
       <c r="H50" t="n">
-        <v>1165.1</v>
+        <v>1140.9</v>
       </c>
       <c r="I50" t="n">
         <v>1143.206624285468</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K50" t="n">
-        <v>32.5</v>
+        <v>29.75</v>
       </c>
       <c r="L50" t="n">
         <v>0.74</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>10.6</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44907</v>
+        <v>44908</v>
       </c>
       <c r="H51" t="n">
-        <v>1206.75</v>
+        <v>1234.95</v>
       </c>
       <c r="I51" t="n">
         <v>1208.623838156214</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.77</v>
+        <v>-8.24</v>
       </c>
       <c r="L51" t="n">
-        <v>8.24</v>
+        <v>8.77</v>
       </c>
       <c r="M51" t="n">
         <v>2.48</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.06</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H52" t="n">
-        <v>1180.15</v>
+        <v>1147.85</v>
       </c>
       <c r="I52" t="n">
         <v>1173.452833242859</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.44</v>
+        <v>-7.05</v>
       </c>
       <c r="L52" t="n">
-        <v>5.24</v>
+        <v>7.45</v>
       </c>
       <c r="M52" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="N52" t="n">
-        <v>2.19</v>
+        <v>2.74</v>
       </c>
       <c r="O52" t="n">
         <v>2.34</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.4</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="H53" t="n">
-        <v>1120.6</v>
+        <v>1174.25</v>
       </c>
       <c r="I53" t="n">
         <v>1160.35815962268</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K53" t="n">
-        <v>2.37</v>
+        <v>-2.3</v>
       </c>
       <c r="L53" t="n">
         <v>10.94</v>
@@ -3462,7 +4097,7 @@
         <v>3.17</v>
       </c>
       <c r="N53" t="n">
-        <v>4.17</v>
+        <v>4.79</v>
       </c>
       <c r="O53" t="n">
         <v>-2.74</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>10.8</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44995</v>
+        <v>44998</v>
       </c>
       <c r="H54" t="n">
-        <v>1144.8</v>
+        <v>1060.1</v>
       </c>
       <c r="I54" t="n">
         <v>1080.978796116963</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.51</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>5.85</v>
+        <v>10.16</v>
       </c>
       <c r="M54" t="n">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="N54" t="n">
-        <v>2.14</v>
+        <v>7.4</v>
       </c>
       <c r="O54" t="n">
         <v>4.79</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.9</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45028</v>
+        <v>45029</v>
       </c>
       <c r="H55" t="n">
-        <v>1074.75</v>
+        <v>1109.3</v>
       </c>
       <c r="I55" t="n">
         <v>1106.47891845994</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.38</v>
+        <v>-4.64</v>
       </c>
       <c r="L55" t="n">
         <v>5.6</v>
@@ -3576,7 +4235,7 @@
         <v>1.98</v>
       </c>
       <c r="N55" t="n">
-        <v>2.3</v>
+        <v>3.21</v>
       </c>
       <c r="O55" t="n">
         <v>-7.4</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>13.8</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45309</v>
+        <v>45310</v>
       </c>
       <c r="H56" t="n">
-        <v>1612.9</v>
+        <v>1561.1</v>
       </c>
       <c r="I56" t="n">
         <v>1589.744538426897</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K56" t="n">
-        <v>45.4</v>
+        <v>40.73</v>
       </c>
       <c r="L56" t="n">
         <v>9.140000000000001</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>10</v>
+      </c>
+      <c r="U56" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45378</v>
+        <v>45379</v>
       </c>
       <c r="H57" t="n">
-        <v>1533.55</v>
+        <v>1553</v>
       </c>
       <c r="I57" t="n">
         <v>1551.39460104663</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K57" t="n">
-        <v>1.76</v>
+        <v>0.52</v>
       </c>
       <c r="L57" t="n">
         <v>4.53</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.03</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45407</v>
+        <v>45408</v>
       </c>
       <c r="H58" t="n">
-        <v>1496.1</v>
+        <v>1446.4</v>
       </c>
       <c r="I58" t="n">
         <v>1464.834328699245</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.66</v>
+        <v>-6.86</v>
       </c>
       <c r="L58" t="n">
-        <v>6.99</v>
+        <v>7.06</v>
       </c>
       <c r="M58" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="O58" t="n">
         <v>1.27</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c r="H59" t="n">
-        <v>1461.85</v>
+        <v>1529.7</v>
       </c>
       <c r="I59" t="n">
         <v>1493.04873390543</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.07</v>
+        <v>-5.76</v>
       </c>
       <c r="L59" t="n">
         <v>6.26</v>
       </c>
       <c r="M59" t="n">
-        <v>1.03</v>
+        <v>3.63</v>
       </c>
       <c r="N59" t="n">
-        <v>2.82</v>
+        <v>4.64</v>
       </c>
       <c r="O59" t="n">
         <v>-3.32</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.84</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H60" t="n">
-        <v>1529.7</v>
+        <v>1391.5</v>
       </c>
       <c r="I60" t="n">
         <v>1409.782615303197</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>2.18</v>
+        <v>10.86</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="O60" t="n">
         <v>4.64</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>14.11</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45534</v>
+        <v>45537</v>
       </c>
       <c r="H61" t="n">
-        <v>1425.25</v>
+        <v>1449.05</v>
       </c>
       <c r="I61" t="n">
         <v>1434.114309650651</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.43</v>
+        <v>-4.14</v>
       </c>
       <c r="L61" t="n">
         <v>11.39</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.77</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45565</v>
+        <v>45566</v>
       </c>
       <c r="H62" t="n">
-        <v>1447.6</v>
+        <v>1409.7</v>
       </c>
       <c r="I62" t="n">
         <v>1414.836563789735</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.1</v>
+        <v>-2.72</v>
       </c>
       <c r="L62" t="n">
         <v>3.38</v>
@@ -3975,7 +4718,7 @@
         <v>1.37</v>
       </c>
       <c r="N62" t="n">
-        <v>1.15</v>
+        <v>2.62</v>
       </c>
       <c r="O62" t="n">
         <v>1.67</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.24</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H63" t="n">
-        <v>991.2</v>
+        <v>1009.4</v>
       </c>
       <c r="I63" t="n">
         <v>1002.396592543594</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K63" t="n">
-        <v>29.69</v>
+        <v>28.4</v>
       </c>
       <c r="L63" t="n">
         <v>2.88</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>10.07</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45716</v>
+        <v>45719</v>
       </c>
       <c r="H64" t="n">
-        <v>990.1</v>
+        <v>984</v>
       </c>
       <c r="I64" t="n">
         <v>986.4402722697475</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.91</v>
+        <v>-2.52</v>
       </c>
       <c r="L64" t="n">
-        <v>3.89</v>
+        <v>6.18</v>
       </c>
       <c r="M64" t="n">
         <v>1.53</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.4</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="H65" t="n">
-        <v>735.9</v>
+        <v>788.25</v>
       </c>
       <c r="I65" t="n">
         <v>770.107139927541</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K65" t="n">
-        <v>25.21</v>
+        <v>19.89</v>
       </c>
       <c r="L65" t="n">
         <v>1.99</v>
@@ -4146,7 +4925,7 @@
         <v>4.86</v>
       </c>
       <c r="N65" t="n">
-        <v>6.73</v>
+        <v>7.11</v>
       </c>
       <c r="O65" t="n">
         <v>-0.62</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>17.13</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H66" t="n">
-        <v>847.9</v>
+        <v>823.7</v>
       </c>
       <c r="I66" t="n">
         <v>824.8553815576901</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>7.57</v>
+        <v>4.5</v>
       </c>
       <c r="L66" t="n">
         <v>7.92</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="H67" t="n">
-        <v>770.05</v>
+        <v>799.75</v>
       </c>
       <c r="I67" t="n">
         <v>774.4514745507049</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K67" t="n">
-        <v>6.51</v>
+        <v>2.91</v>
       </c>
       <c r="L67" t="n">
         <v>3.04</v>
@@ -4260,7 +5063,7 @@
         <v>1.98</v>
       </c>
       <c r="N67" t="n">
-        <v>2.85</v>
+        <v>3.86</v>
       </c>
       <c r="O67" t="n">
         <v>-2.85</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H68" t="n">
-        <v>917.85</v>
+        <v>881.2</v>
       </c>
       <c r="I68" t="n">
         <v>891.8288903634858</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K68" t="n">
-        <v>14.77</v>
+        <v>10.18</v>
       </c>
       <c r="L68" t="n">
         <v>3.41</v>
       </c>
       <c r="M68" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="N68" t="n">
         <v>4.7</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H69" t="n">
-        <v>856.4</v>
+        <v>870.1</v>
       </c>
       <c r="I69" t="n">
         <v>862.2195386597001</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K69" t="n">
-        <v>2.81</v>
+        <v>1.26</v>
       </c>
       <c r="L69" t="n">
         <v>2.98</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="H70" t="n">
-        <v>1006.65</v>
+        <v>991.95</v>
       </c>
       <c r="I70" t="n">
         <v>992.1567646553773</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K70" t="n">
-        <v>15.69</v>
+        <v>14</v>
       </c>
       <c r="L70" t="n">
         <v>3.57</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>64</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.4</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123.4</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.8</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.1</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.3</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.84</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>70.08</v>
+        <v>68.01000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.22</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.96</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.94</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="25">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.89</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="27">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
